--- a/artfynd/A 2810-2020 artfynd.xlsx
+++ b/artfynd/A 2810-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118898571</v>
+        <v>118898819</v>
       </c>
       <c r="B2" t="n">
         <v>97846</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689067</v>
+        <v>689073</v>
       </c>
       <c r="R2" t="n">
-        <v>6633002</v>
+        <v>6633003</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>En blomstängel</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118898819</v>
+        <v>118898571</v>
       </c>
       <c r="B3" t="n">
         <v>97846</v>
@@ -836,7 +841,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -846,7 +851,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -855,10 +860,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689073</v>
+        <v>689067</v>
       </c>
       <c r="R3" t="n">
-        <v>6633003</v>
+        <v>6633002</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,12 +905,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>En blomstängel</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,7 +932,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118900851</v>
+        <v>118901418</v>
       </c>
       <c r="B4" t="n">
         <v>97846</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689083</v>
+        <v>689029</v>
       </c>
       <c r="R4" t="n">
-        <v>6633059</v>
+        <v>6632933</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1160,7 +1160,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118899090</v>
+        <v>118900913</v>
       </c>
       <c r="B6" t="n">
         <v>97846</v>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>689069</v>
+        <v>689082</v>
       </c>
       <c r="R6" t="n">
-        <v>6632967</v>
+        <v>6633049</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,7 +1286,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118898957</v>
+        <v>118900851</v>
       </c>
       <c r="B7" t="n">
         <v>97846</v>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1329,16 +1329,21 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Trollmossen (Trollmossen), Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>689073</v>
+        <v>689083</v>
       </c>
       <c r="R7" t="n">
-        <v>6632988</v>
+        <v>6633059</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,7 +1375,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1380,7 +1385,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,7 +1412,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118900913</v>
+        <v>118899227</v>
       </c>
       <c r="B8" t="n">
         <v>97846</v>
@@ -1442,7 +1447,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1461,10 +1466,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>689082</v>
+        <v>689069</v>
       </c>
       <c r="R8" t="n">
-        <v>6633049</v>
+        <v>6632969</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1496,7 +1501,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1506,7 +1511,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1659,7 +1664,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118901418</v>
+        <v>118898957</v>
       </c>
       <c r="B10" t="n">
         <v>97846</v>
@@ -1694,7 +1699,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1702,21 +1707,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Trollmossen (Trollmossen), Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>689029</v>
+        <v>689073</v>
       </c>
       <c r="R10" t="n">
-        <v>6632933</v>
+        <v>6632988</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1785,7 +1785,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118900841</v>
+        <v>118899090</v>
       </c>
       <c r="B11" t="n">
         <v>97846</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1833,18 +1833,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Barrnaturskog nordväst om Gårdagsmossbergen (Gårdagsmossbergen), Upl</t>
+          <t>Trollmossen (Trollmossen), Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>689085</v>
+        <v>689069</v>
       </c>
       <c r="R11" t="n">
-        <v>6633046</v>
+        <v>6632967</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1874,37 +1872,46 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118899227</v>
+        <v>118900841</v>
       </c>
       <c r="B12" t="n">
         <v>97846</v>
@@ -1939,7 +1946,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1952,16 +1959,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Trollmossen (Trollmossen), Upl</t>
+          <t>Barrnaturskog nordväst om Gårdagsmossbergen (Gårdagsmossbergen), Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>689069</v>
+        <v>689085</v>
       </c>
       <c r="R12" t="n">
-        <v>6632969</v>
+        <v>6633046</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1991,39 +2000,30 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2033,7 +2033,7 @@
         <v>118900985</v>
       </c>
       <c r="B13" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2078,6 +2078,8 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Trollmossen (Trollmossen), Upl</t>
@@ -2138,6 +2140,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 2810-2020 artfynd.xlsx
+++ b/artfynd/A 2810-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118898819</v>
+        <v>118898571</v>
       </c>
       <c r="B2" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689073</v>
+        <v>689067</v>
       </c>
       <c r="R2" t="n">
-        <v>6633003</v>
+        <v>6633002</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>En blomstängel</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118898571</v>
+        <v>118899090</v>
       </c>
       <c r="B3" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -841,7 +836,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -860,10 +855,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689067</v>
+        <v>689069</v>
       </c>
       <c r="R3" t="n">
-        <v>6633002</v>
+        <v>6632967</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,7 +930,7 @@
         <v>118901418</v>
       </c>
       <c r="B4" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1058,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118900818</v>
+        <v>118900841</v>
       </c>
       <c r="B5" t="n">
-        <v>104940</v>
+        <v>97853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,38 +1065,54 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Barrnaturskog nordväst om Gårdagsmossbergen (Gårdagsmossbergen), Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689088</v>
+        <v>689085</v>
       </c>
       <c r="R5" t="n">
-        <v>6633056</v>
+        <v>6633046</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1142,6 +1153,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1160,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118900913</v>
+        <v>118899227</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1195,7 +1207,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1214,10 +1226,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>689082</v>
+        <v>689069</v>
       </c>
       <c r="R6" t="n">
-        <v>6633049</v>
+        <v>6632969</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1249,7 +1261,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1259,7 +1271,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1301,7 @@
         <v>118900851</v>
       </c>
       <c r="B7" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1412,10 +1424,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118899227</v>
+        <v>118898819</v>
       </c>
       <c r="B8" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1447,7 +1459,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1457,7 +1469,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1466,10 +1478,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>689069</v>
+        <v>689073</v>
       </c>
       <c r="R8" t="n">
-        <v>6632969</v>
+        <v>6633003</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,7 +1513,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1511,7 +1523,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En blomstängel</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1538,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118901164</v>
+        <v>118900913</v>
       </c>
       <c r="B9" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1573,7 +1590,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1592,10 +1609,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>689035</v>
+        <v>689082</v>
       </c>
       <c r="R9" t="n">
-        <v>6632941</v>
+        <v>6633049</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1627,7 +1644,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1637,7 +1654,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,10 +1681,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118898957</v>
+        <v>118900818</v>
       </c>
       <c r="B10" t="n">
-        <v>97846</v>
+        <v>104947</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1676,47 +1693,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Trollmossen (Trollmossen), Upl</t>
+          <t>Barrnaturskog nordväst om Gårdagsmossbergen (Gårdagsmossbergen), Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>689073</v>
+        <v>689088</v>
       </c>
       <c r="R10" t="n">
-        <v>6632988</v>
+        <v>6633056</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1746,19 +1754,9 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1773,22 +1771,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118899090</v>
+        <v>118898957</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1820,7 +1818,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1828,21 +1826,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Trollmossen (Trollmossen), Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>689069</v>
+        <v>689073</v>
       </c>
       <c r="R11" t="n">
-        <v>6632967</v>
+        <v>6632988</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1874,7 +1867,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1884,7 +1877,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1911,10 +1904,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118900841</v>
+        <v>118901164</v>
       </c>
       <c r="B12" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1946,7 +1939,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1959,18 +1952,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Barrnaturskog nordväst om Gårdagsmossbergen (Gårdagsmossbergen), Upl</t>
+          <t>Trollmossen (Trollmossen), Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>689085</v>
+        <v>689035</v>
       </c>
       <c r="R12" t="n">
-        <v>6633046</v>
+        <v>6632941</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2000,30 +1991,39 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 2810-2020 artfynd.xlsx
+++ b/artfynd/A 2810-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118898571</v>
+        <v>118900818</v>
       </c>
       <c r="B2" t="n">
-        <v>97853</v>
+        <v>104947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Trollmossen (Trollmossen), Upl</t>
+          <t>Barrnaturskog nordväst om Gårdagsmossbergen (Gårdagsmossbergen), Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689067</v>
+        <v>689088</v>
       </c>
       <c r="R2" t="n">
-        <v>6633002</v>
+        <v>6633056</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,19 +748,9 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118899090</v>
+        <v>118901418</v>
       </c>
       <c r="B3" t="n">
         <v>97853</v>
@@ -855,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>689069</v>
+        <v>689029</v>
       </c>
       <c r="R3" t="n">
-        <v>6632967</v>
+        <v>6632933</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118901418</v>
+        <v>118900851</v>
       </c>
       <c r="B4" t="n">
         <v>97853</v>
@@ -962,7 +938,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -981,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>689029</v>
+        <v>689083</v>
       </c>
       <c r="R4" t="n">
-        <v>6632933</v>
+        <v>6633059</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1026,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1046,14 +1022,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118900841</v>
+        <v>118898571</v>
       </c>
       <c r="B5" t="n">
         <v>97853</v>
@@ -1088,7 +1064,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1101,18 +1077,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Barrnaturskog nordväst om Gårdagsmossbergen (Gårdagsmossbergen), Upl</t>
+          <t>Trollmossen (Trollmossen), Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>689085</v>
+        <v>689067</v>
       </c>
       <c r="R5" t="n">
-        <v>6633046</v>
+        <v>6633002</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1142,37 +1116,46 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118899227</v>
+        <v>118900841</v>
       </c>
       <c r="B6" t="n">
         <v>97853</v>
@@ -1207,7 +1190,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1220,16 +1203,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Trollmossen (Trollmossen), Upl</t>
+          <t>Barrnaturskog nordväst om Gårdagsmossbergen (Gårdagsmossbergen), Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>689069</v>
+        <v>689085</v>
       </c>
       <c r="R6" t="n">
-        <v>6632969</v>
+        <v>6633046</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1259,46 +1244,37 @@
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-04</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118900851</v>
+        <v>118901164</v>
       </c>
       <c r="B7" t="n">
         <v>97853</v>
@@ -1333,7 +1309,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1352,10 +1328,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>689083</v>
+        <v>689035</v>
       </c>
       <c r="R7" t="n">
-        <v>6633059</v>
+        <v>6632941</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1387,7 +1363,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1397,7 +1373,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1424,7 +1400,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118898819</v>
+        <v>118899090</v>
       </c>
       <c r="B8" t="n">
         <v>97853</v>
@@ -1459,7 +1435,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1469,7 +1445,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1478,10 +1454,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>689073</v>
+        <v>689069</v>
       </c>
       <c r="R8" t="n">
-        <v>6633003</v>
+        <v>6632967</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1513,7 +1489,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1523,12 +1499,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:57</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En blomstängel</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1555,7 +1526,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118900913</v>
+        <v>118899227</v>
       </c>
       <c r="B9" t="n">
         <v>97853</v>
@@ -1590,7 +1561,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1609,10 +1580,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>689082</v>
+        <v>689069</v>
       </c>
       <c r="R9" t="n">
-        <v>6633049</v>
+        <v>6632969</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1644,7 +1615,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1654,7 +1625,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1681,10 +1652,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118900818</v>
+        <v>118900913</v>
       </c>
       <c r="B10" t="n">
-        <v>104947</v>
+        <v>97853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1693,38 +1664,52 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Barrnaturskog nordväst om Gårdagsmossbergen (Gårdagsmossbergen), Upl</t>
+          <t>Trollmossen (Trollmossen), Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>689088</v>
+        <v>689082</v>
       </c>
       <c r="R10" t="n">
-        <v>6633056</v>
+        <v>6633049</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1754,9 +1739,19 @@
           <t>2024-08-04</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1771,12 +1766,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1897,14 +1892,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118901164</v>
+        <v>118898819</v>
       </c>
       <c r="B12" t="n">
         <v>97853</v>
@@ -1939,7 +1934,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1949,7 +1944,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1958,10 +1953,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>689035</v>
+        <v>689073</v>
       </c>
       <c r="R12" t="n">
-        <v>6632941</v>
+        <v>6633003</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1993,7 +1988,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2003,7 +1998,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>En blomstängel</t>
         </is>
       </c>
       <c r="AD12" t="b">
